--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496886.5941934994</v>
+        <v>496887</v>
       </c>
       <c r="R2" t="n">
-        <v>6443581.816500953</v>
+        <v>6443582</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496886.5941934994</v>
+        <v>496887</v>
       </c>
       <c r="R3" t="n">
-        <v>6443581.816500953</v>
+        <v>6443582</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,12 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496886.5941934994</v>
+        <v>496887</v>
       </c>
       <c r="R4" t="n">
-        <v>6443581.816500953</v>
+        <v>6443582</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -990,19 +955,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74601346</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74860936</v>
       </c>
       <c r="B4" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74601346</v>
+        <v>74499125</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,23 +792,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -856,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Lycopodium annotinum. LEG: Lars Theng</t>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Huperzia selago. LEG: Lars Theng</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74860936</v>
+        <v>74601346</v>
       </c>
       <c r="B4" t="n">
-        <v>105732</v>
+        <v>97540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +894,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Pyrola chlorantha. LEG: Lars Theng</t>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Lycopodium annotinum. LEG: Lars Theng</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,6 +982,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74860936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105732</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L1 Lyngsbergen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496887</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6443582</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1986-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Pyrola chlorantha. LEG: Lars Theng</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74468896</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74499125</v>
+        <v>74860936</v>
       </c>
       <c r="B3" t="n">
-        <v>97534</v>
+        <v>106243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,19 +792,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Huperzia selago. LEG: Lars Theng</t>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Pyrola chlorantha. LEG: Lars Theng</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74601346</v>
+        <v>74499125</v>
       </c>
       <c r="B4" t="n">
-        <v>97540</v>
+        <v>97977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,23 +898,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Lycopodium annotinum. LEG: Lars Theng</t>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Huperzia selago. LEG: Lars Theng</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74860936</v>
+        <v>74601346</v>
       </c>
       <c r="B5" t="n">
-        <v>105732</v>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Pyrola chlorantha. LEG: Lars Theng</t>
+          <t>Smålands flora 2007: KOO: 7E9j 0844. SOM: Lycopodium annotinum. LEG: Lars Theng</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4529-2024 artfynd.xlsx
+++ b/artfynd/A 4529-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74468896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74860936</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74499125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74601346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>